--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios186.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios186.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.70119579146013</v>
+        <v>28.55626608795042</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.04781087892536</v>
+        <v>27.84941311166598</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.88492706402932</v>
+        <v>32.43258862148141</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.58929295609729</v>
+        <v>27.98398142674121</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.04965930338082</v>
+        <v>30.40691128464054</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.27538975003844</v>
+        <v>29.82538254770158</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.6931304998584</v>
+        <v>28.70893060933341</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.11625228609227</v>
+        <v>27.63271103713592</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.84856525370461</v>
+        <v>32.64537635880405</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.87177139280271</v>
+        <v>27.12063792233659</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32.36139072756409</v>
+        <v>30.86785843954243</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.31156617112162</v>
+        <v>30.16271255989571</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.00661661513861</v>
+        <v>28.6025654535876</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.06402107825391</v>
+        <v>27.7433054032563</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.97727965117022</v>
+        <v>32.72500547632124</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.50722929161716</v>
+        <v>27.54468084814476</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.87809502425371</v>
+        <v>30.32975661494646</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19.21810778407723</v>
+        <v>29.4486121378196</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.00276167477465</v>
+        <v>28.75239554349444</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.05794781825148</v>
+        <v>27.78478540098157</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.65603570321258</v>
+        <v>32.07540932259478</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.73635476820084</v>
+        <v>27.31215740181358</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.37729912501848</v>
+        <v>30.80550979926488</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19.38732220682815</v>
+        <v>29.4836886314348</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.89331646192489</v>
+        <v>28.57701894679837</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25.08523741937086</v>
+        <v>27.66110732720211</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.77564466501198</v>
+        <v>32.02977785897603</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.22165630016945</v>
+        <v>27.03024718556291</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32.29657189694633</v>
+        <v>30.62265704391709</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.15722577157833</v>
+        <v>29.14623878923184</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.63467347998091</v>
+        <v>28.43840208253999</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>24.74095249888678</v>
+        <v>27.84595438768139</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.0077343591424</v>
+        <v>32.77134885196212</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29.93921822750792</v>
+        <v>27.08035958220795</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32.56747881702336</v>
+        <v>30.21878718058378</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19.42363957690345</v>
+        <v>29.52058575994498</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.84702493116487</v>
+        <v>26.42074949941578</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27.55220832065831</v>
+        <v>32.02795340016019</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25.37154279221897</v>
+        <v>32.76799369545867</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26.14395693913534</v>
+        <v>27.16232484929958</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.75360210040571</v>
+        <v>29.42946841202916</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>29.54327675364101</v>
+        <v>32.3918142519418</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28.73679647920827</v>
+        <v>26.59499363529143</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>27.42679455687624</v>
+        <v>31.36110205246021</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25.37631069347572</v>
+        <v>32.39755680076375</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26.27811033509759</v>
+        <v>27.8934190819741</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.08510931438159</v>
+        <v>28.47713302798241</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>29.02622741841714</v>
+        <v>32.57286994991422</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>29.14400224184758</v>
+        <v>26.63438455529674</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27.12409615859836</v>
+        <v>31.474325905975</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>24.82900679303346</v>
+        <v>32.055647976804</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.1840139176494</v>
+        <v>27.89110922626523</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.77491446341256</v>
+        <v>28.23017061004369</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>29.09979028692377</v>
+        <v>31.93737726275074</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>28.38525745536229</v>
+        <v>26.79132008427407</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>26.84397840371176</v>
+        <v>31.35021922562171</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>24.71018086657252</v>
+        <v>33.08194766911305</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.78721532996148</v>
+        <v>27.52539269865023</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>29.17474532611923</v>
+        <v>28.41977849335034</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>29.58503063497382</v>
+        <v>32.64786690153565</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>28.87060781005523</v>
+        <v>26.48150104078482</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>27.71486154044862</v>
+        <v>32.39034758398876</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>24.46458391177651</v>
+        <v>33.50967755100687</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>25.95196957779746</v>
+        <v>27.98530749723255</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>28.72891525216254</v>
+        <v>28.53537630545327</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>29.17591987010475</v>
+        <v>32.68886016036507</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>28.44892831603993</v>
+        <v>26.71595543026118</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.09404115683152</v>
+        <v>31.99134411247432</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>24.96039091851481</v>
+        <v>32.70678463395713</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>26.28439678487816</v>
+        <v>27.44799589875725</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.75234203241855</v>
+        <v>27.98718880246167</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>28.67588266749141</v>
+        <v>33.11636072041401</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>23.2198762478881</v>
+        <v>31.40828281954996</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>32.79530607597964</v>
+        <v>28.16015852084124</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27.81807739351883</v>
+        <v>31.96345624085305</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27.56650279056496</v>
+        <v>31.46120910795848</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.55990809727746</v>
+        <v>29.16027939205444</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>20.10782603752793</v>
+        <v>26.99086515515645</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>23.42322300113199</v>
+        <v>31.45135185673148</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>32.62255818964524</v>
+        <v>28.1345469026725</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>27.65024651257172</v>
+        <v>31.26018812030889</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.51659030971683</v>
+        <v>31.43793805218458</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>32.6702762402808</v>
+        <v>28.76397147287048</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>20.16162769376982</v>
+        <v>26.96924533325435</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>23.66539675078774</v>
+        <v>30.8201451621284</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>33.110260260716</v>
+        <v>27.877370740372</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>27.86750081082245</v>
+        <v>31.60746872210599</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.65912000693534</v>
+        <v>31.65830669888458</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.84501059490114</v>
+        <v>29.04637959811466</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>20.47831816663642</v>
+        <v>26.9578981657443</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>23.48619540488054</v>
+        <v>32.09594557302062</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>33.50526889569767</v>
+        <v>28.26529141673795</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>28.01515935634883</v>
+        <v>31.44503557688904</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>28.13619782075902</v>
+        <v>31.73083566819666</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>32.76420571416704</v>
+        <v>29.28692664160537</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>20.47526007964668</v>
+        <v>26.95666162821018</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>23.265864115535</v>
+        <v>31.52169969465827</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>32.82526195643256</v>
+        <v>28.34131562312731</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>27.98440733324426</v>
+        <v>31.47302211735557</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>27.97685305883983</v>
+        <v>31.73392440142327</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>32.88659557802617</v>
+        <v>29.45477631199092</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>20.56164068909605</v>
+        <v>27.03560475689449</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>23.118536418465</v>
+        <v>30.99863267974518</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>32.65508573354666</v>
+        <v>28.13931753302491</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>27.95100126499488</v>
+        <v>30.8973352873353</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>27.67950745844552</v>
+        <v>31.74233183914235</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>33.82572517889764</v>
+        <v>29.37161213864646</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>20.44273074801417</v>
+        <v>26.6082686694149</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>27.05116135987168</v>
+        <v>30.71862528476997</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>27.51840489146641</v>
+        <v>28.35715771091597</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>31.17527131822842</v>
+        <v>20.8001130673194</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>27.87820971775817</v>
+        <v>25.69759572072565</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>31.38527053309775</v>
+        <v>25.44086288380297</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>23.59240128693255</v>
+        <v>28.0633936468089</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>26.99841859539096</v>
+        <v>30.21090074933132</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>28.03283119495847</v>
+        <v>27.80010798630628</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>31.75939111425162</v>
+        <v>20.74455556567689</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>27.94005096311235</v>
+        <v>25.4129744857683</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>30.92967688921896</v>
+        <v>26.11351580810983</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>23.82827062070966</v>
+        <v>27.66297308250603</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>27.49314842770108</v>
+        <v>31.12469204985217</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>28.0398837863583</v>
+        <v>28.27373130908725</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>31.5557493771611</v>
+        <v>20.75858316106341</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>28.26623614180424</v>
+        <v>25.09880404114421</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>31.36690007053506</v>
+        <v>26.22889989434043</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>23.8495063515922</v>
+        <v>27.83412486659958</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>26.88806531274685</v>
+        <v>30.48521862573287</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27.7418323043687</v>
+        <v>28.25607702331235</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>31.74217115983108</v>
+        <v>20.69560404479112</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>27.70553839048647</v>
+        <v>25.15801111556379</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>31.08010008553439</v>
+        <v>26.45831203254161</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>23.72374742019467</v>
+        <v>28.42901509389397</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.01100455056948</v>
+        <v>30.85827881782108</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>27.84054946765778</v>
+        <v>28.20130327614043</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>31.18369879133925</v>
+        <v>20.64346020572874</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>28.34873542133845</v>
+        <v>24.97959470818142</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>30.94584844160103</v>
+        <v>25.9544571976876</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>23.99778510810548</v>
+        <v>27.95019918521675</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>26.86530458210916</v>
+        <v>30.49601988878233</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.16420220643528</v>
+        <v>27.99357746241873</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>31.4002014679144</v>
+        <v>20.08563938569328</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>27.79885081198631</v>
+        <v>25.09446371834545</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>31.00229965680807</v>
+        <v>26.16419706067911</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>23.30214479948783</v>
+        <v>28.40579658823923</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>30.40929933059077</v>
+        <v>25.3241994395216</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>33.01533313356882</v>
+        <v>28.59095335647444</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>30.05735314154598</v>
+        <v>33.50847742900192</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>27.78767176120628</v>
+        <v>31.83129938039944</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>32.17983052835005</v>
+        <v>24.65334802261916</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>28.24462750025861</v>
+        <v>21.00596401354621</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>29.97703652217955</v>
+        <v>25.86970905173878</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>32.23169151428171</v>
+        <v>28.17277492365872</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>29.82184215194604</v>
+        <v>32.77831935104003</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>27.7273067268591</v>
+        <v>32.08720278040408</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>32.29901227566382</v>
+        <v>24.51130876848339</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>28.46627210628156</v>
+        <v>21.00122888742695</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>30.5958740966482</v>
+        <v>25.71259246166484</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>32.60462886528609</v>
+        <v>28.2731746539857</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>29.46997996589717</v>
+        <v>32.69053336431764</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>27.8863633140783</v>
+        <v>31.83773314302143</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>32.19466574770625</v>
+        <v>24.39266937621062</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>27.57750066349238</v>
+        <v>20.95344028649011</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>30.15810438895649</v>
+        <v>25.8898146169992</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>32.47032184930362</v>
+        <v>28.75863820900248</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>29.91792016040429</v>
+        <v>33.32116421056203</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>27.54881459154013</v>
+        <v>32.06879140751391</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>32.01425938458285</v>
+        <v>24.38142707537655</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>28.1928351260703</v>
+        <v>20.83362421941892</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>30.36344171417782</v>
+        <v>25.25932045713005</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>32.46203664163215</v>
+        <v>28.34056688144358</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>29.69160904307244</v>
+        <v>33.13019867626557</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>27.47191229565506</v>
+        <v>31.62818748556104</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>32.1481947362921</v>
+        <v>24.52926163377356</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>28.41366584298434</v>
+        <v>20.97220685536335</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>30.17748288658992</v>
+        <v>25.46380743852833</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>33.19346346493298</v>
+        <v>28.87025780838924</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>29.78854314980556</v>
+        <v>32.3288670306021</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>28.19688521100382</v>
+        <v>31.87497167216706</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>31.82082185878582</v>
+        <v>23.91169105721334</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>27.67976096304543</v>
+        <v>21.06319359176564</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>30.59165032247752</v>
+        <v>26.95197147999682</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>31.19080041566141</v>
+        <v>24.39264923746846</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>30.31788693176873</v>
+        <v>19.31101465507823</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>27.46641746544914</v>
+        <v>27.49463858001006</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>31.91459978115812</v>
+        <v>32.13574046618448</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>24.38064092359721</v>
+        <v>29.61944797820186</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>30.37698104336334</v>
+        <v>26.67356751733476</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>31.37533040485475</v>
+        <v>24.63574630290828</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>30.36329461372841</v>
+        <v>19.35978410479513</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>27.81257062145118</v>
+        <v>28.28622821828975</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>31.85161168626299</v>
+        <v>32.20276467918486</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>24.42211527678449</v>
+        <v>29.36864206725482</v>
       </c>
     </row>
     <row r="194">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>30.11764845310407</v>
+        <v>26.56071939043061</v>
       </c>
     </row>
     <row r="195">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>30.99833818215043</v>
+        <v>24.51109954690234</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>29.30091747834994</v>
+        <v>19.82498457591882</v>
       </c>
     </row>
     <row r="197">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>27.48079522850299</v>
+        <v>28.16857256908155</v>
       </c>
     </row>
     <row r="198">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>31.89949833167562</v>
+        <v>32.07467917760578</v>
       </c>
     </row>
     <row r="199">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>24.64406327753549</v>
+        <v>30.22813139686818</v>
       </c>
     </row>
     <row r="200">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>30.38724050532792</v>
+        <v>27.13649647717755</v>
       </c>
     </row>
     <row r="201">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>31.22164271162363</v>
+        <v>24.66968640184323</v>
       </c>
     </row>
     <row r="202">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>29.64682440195691</v>
+        <v>19.46985789916281</v>
       </c>
     </row>
     <row r="203">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>27.62824397437494</v>
+        <v>27.86829512927288</v>
       </c>
     </row>
     <row r="204">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>31.38944521626535</v>
+        <v>31.80932420501084</v>
       </c>
     </row>
     <row r="205">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>24.20982379606805</v>
+        <v>30.23608266281915</v>
       </c>
     </row>
     <row r="206">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>30.41207658202726</v>
+        <v>26.47890612329697</v>
       </c>
     </row>
     <row r="207">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>31.51055941587225</v>
+        <v>24.94143696570824</v>
       </c>
     </row>
     <row r="208">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>30.41996639762522</v>
+        <v>19.68512596631729</v>
       </c>
     </row>
     <row r="209">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>27.64899569756428</v>
+        <v>27.88437711068842</v>
       </c>
     </row>
     <row r="210">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>31.91940198315133</v>
+        <v>32.6966030932609</v>
       </c>
     </row>
     <row r="211">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>24.33104841182224</v>
+        <v>29.25735790009965</v>
       </c>
     </row>
     <row r="212">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>30.30335737461017</v>
+        <v>26.72678645911269</v>
       </c>
     </row>
     <row r="213">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>31.24644092558412</v>
+        <v>24.60581001106069</v>
       </c>
     </row>
     <row r="214">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>29.887595417799</v>
+        <v>19.73792107977135</v>
       </c>
     </row>
     <row r="215">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>27.80789952904423</v>
+        <v>28.06853817311999</v>
       </c>
     </row>
     <row r="216">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>31.80160382774906</v>
+        <v>31.56057559126527</v>
       </c>
     </row>
     <row r="217">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>24.708240244765</v>
+        <v>30.08911512399897</v>
       </c>
     </row>
     <row r="218">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>26.57607954690327</v>
+        <v>27.75812314393033</v>
       </c>
     </row>
     <row r="219">
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>26.78957875996311</v>
+        <v>26.95661543169633</v>
       </c>
     </row>
     <row r="220">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>25.5530343240991</v>
+        <v>27.29137414561603</v>
       </c>
     </row>
     <row r="221">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>23.14782827685418</v>
+        <v>27.33622117552736</v>
       </c>
     </row>
     <row r="222">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>31.99039282203669</v>
+        <v>32.37641444676707</v>
       </c>
     </row>
     <row r="223">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>15.05040906784875</v>
+        <v>27.71997325100699</v>
       </c>
     </row>
     <row r="224">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>26.96570402520163</v>
+        <v>27.5315761098081</v>
       </c>
     </row>
     <row r="225">
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>27.41148099985839</v>
+        <v>27.11596910215448</v>
       </c>
     </row>
     <row r="226">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>26.19530643993181</v>
+        <v>26.94545777302218</v>
       </c>
     </row>
     <row r="227">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>23.54114759573619</v>
+        <v>27.78964363284733</v>
       </c>
     </row>
     <row r="228">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>32.33929777518573</v>
+        <v>31.80768467113334</v>
       </c>
     </row>
     <row r="229">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>15.14937326110416</v>
+        <v>27.68702528556781</v>
       </c>
     </row>
     <row r="230">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>26.4779846363003</v>
+        <v>27.12701995628633</v>
       </c>
     </row>
     <row r="231">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>27.36461787568359</v>
+        <v>27.2524264993875</v>
       </c>
     </row>
     <row r="232">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>25.55412378882477</v>
+        <v>27.38546543555664</v>
       </c>
     </row>
     <row r="233">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>22.99502646902809</v>
+        <v>27.80795181884823</v>
       </c>
     </row>
     <row r="234">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>33.6521830743797</v>
+        <v>32.71147528267698</v>
       </c>
     </row>
     <row r="235">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>15.1859656130315</v>
+        <v>27.96837891949816</v>
       </c>
     </row>
     <row r="236">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>26.23734550850226</v>
+        <v>27.17926062959523</v>
       </c>
     </row>
     <row r="237">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>27.27629593187313</v>
+        <v>27.22281508459346</v>
       </c>
     </row>
     <row r="238">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>25.64012785563328</v>
+        <v>27.93788047661539</v>
       </c>
     </row>
     <row r="239">
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>23.37622745190291</v>
+        <v>27.72922680665125</v>
       </c>
     </row>
     <row r="240">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>33.00029794366006</v>
+        <v>32.16219899312232</v>
       </c>
     </row>
     <row r="241">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>15.1884902279253</v>
+        <v>27.65636295017081</v>
       </c>
     </row>
     <row r="242">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>26.01702873471186</v>
+        <v>27.51803515219182</v>
       </c>
     </row>
     <row r="243">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>27.20137695738611</v>
+        <v>26.91821808825268</v>
       </c>
     </row>
     <row r="244">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>25.58315226972152</v>
+        <v>27.62516404767249</v>
       </c>
     </row>
     <row r="245">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>23.68001907740082</v>
+        <v>27.85808411633078</v>
       </c>
     </row>
     <row r="246">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>32.96255995354186</v>
+        <v>31.9990147437553</v>
       </c>
     </row>
     <row r="247">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>15.22378264193961</v>
+        <v>27.65260603122686</v>
       </c>
     </row>
     <row r="248">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>25.98648726011036</v>
+        <v>27.46753907817089</v>
       </c>
     </row>
     <row r="249">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>26.91141801895022</v>
+        <v>26.80241714512007</v>
       </c>
     </row>
     <row r="250">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>25.70640226682438</v>
+        <v>26.99966265265041</v>
       </c>
     </row>
     <row r="251">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>23.42609648185424</v>
+        <v>27.34561715034331</v>
       </c>
     </row>
     <row r="252">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>32.45894182618335</v>
+        <v>32.41287049563257</v>
       </c>
     </row>
     <row r="253">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>15.13440939436071</v>
+        <v>27.55166879667716</v>
       </c>
     </row>
     <row r="254">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>36.65438644629004</v>
+        <v>27.64102011632193</v>
       </c>
     </row>
     <row r="255">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>32.19772748854046</v>
+        <v>22.71206343843251</v>
       </c>
     </row>
     <row r="256">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>24.38680271288828</v>
+        <v>32.08428491747058</v>
       </c>
     </row>
     <row r="257">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>27.71773167146981</v>
+        <v>26.17199225629061</v>
       </c>
     </row>
     <row r="258">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>30.71510100404326</v>
+        <v>31.38398338509893</v>
       </c>
     </row>
     <row r="259">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>23.98848020854803</v>
+        <v>18.48299686600942</v>
       </c>
     </row>
     <row r="260">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>36.57289187159083</v>
+        <v>28.35597032567315</v>
       </c>
     </row>
     <row r="261">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>32.26338181176531</v>
+        <v>22.88078547776587</v>
       </c>
     </row>
     <row r="262">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>25.03866103522879</v>
+        <v>31.69052152717869</v>
       </c>
     </row>
     <row r="263">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>28.39015300077457</v>
+        <v>26.10321046373799</v>
       </c>
     </row>
     <row r="264">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>31.29916460612721</v>
+        <v>30.68486534099254</v>
       </c>
     </row>
     <row r="265">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>23.68864497534127</v>
+        <v>18.4685707999386</v>
       </c>
     </row>
     <row r="266">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>36.69764378269979</v>
+        <v>28.02871746363493</v>
       </c>
     </row>
     <row r="267">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>31.99147238744569</v>
+        <v>22.94088765069288</v>
       </c>
     </row>
     <row r="268">
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>24.92184340244836</v>
+        <v>31.71560208416311</v>
       </c>
     </row>
     <row r="269">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>27.90474991243091</v>
+        <v>26.79194004276131</v>
       </c>
     </row>
     <row r="270">
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>31.08003584957379</v>
+        <v>31.01916638322139</v>
       </c>
     </row>
     <row r="271">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>23.80189747347862</v>
+        <v>18.21436508652027</v>
       </c>
     </row>
     <row r="272">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>37.09118379499972</v>
+        <v>28.24732448096532</v>
       </c>
     </row>
     <row r="273">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>32.61081718786441</v>
+        <v>22.93985196370081</v>
       </c>
     </row>
     <row r="274">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>25.44744916867763</v>
+        <v>31.92000740057284</v>
       </c>
     </row>
     <row r="275">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>28.06133246315135</v>
+        <v>25.95772301175258</v>
       </c>
     </row>
     <row r="276">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>31.24874795014338</v>
+        <v>31.19489922542591</v>
       </c>
     </row>
     <row r="277">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>23.61892302480981</v>
+        <v>18.8252199870595</v>
       </c>
     </row>
     <row r="278">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>37.30991638369019</v>
+        <v>27.96499033801679</v>
       </c>
     </row>
     <row r="279">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>32.54712337533682</v>
+        <v>22.46622981968875</v>
       </c>
     </row>
     <row r="280">
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>25.23398911864891</v>
+        <v>30.74646041004182</v>
       </c>
     </row>
     <row r="281">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>28.05275819372694</v>
+        <v>26.17925876042851</v>
       </c>
     </row>
     <row r="282">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>30.70233335980943</v>
+        <v>30.76632621749415</v>
       </c>
     </row>
     <row r="283">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>23.37173952870317</v>
+        <v>18.50682041944623</v>
       </c>
     </row>
     <row r="284">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>36.85820621734276</v>
+        <v>27.68291398630211</v>
       </c>
     </row>
     <row r="285">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>32.69897227383291</v>
+        <v>22.6005585848003</v>
       </c>
     </row>
     <row r="286">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>24.90466031804677</v>
+        <v>31.60251235233184</v>
       </c>
     </row>
     <row r="287">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>28.2464364783233</v>
+        <v>25.90296904967585</v>
       </c>
     </row>
     <row r="288">
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>31.16977184702849</v>
+        <v>31.3138732303999</v>
       </c>
     </row>
     <row r="289">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>23.63503440007762</v>
+        <v>18.63156168253625</v>
       </c>
     </row>
   </sheetData>
